--- a/Analytics/свойста_казино.xlsx
+++ b/Analytics/свойста_казино.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\Brackeys-Game-Jam\Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B073C3F9-E5A3-42E8-ADD9-A981D3C65440}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDCD76D-6A1A-443A-8DD0-22B2BF76073B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{28298931-A808-4930-B925-C5E4854C6B70}"/>
   </bookViews>
